--- a/proposals/2026-12_nmk-museum-web-maint/요구사항_수용여부_조견표.xlsx
+++ b/proposals/2026-12_nmk-museum-web-maint/요구사항_수용여부_조견표.xlsx
@@ -827,7 +827,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Ⅱ. 전략 및 방법론 &gt; 3.4.2 웹 접근성 품질인증 · DB 표준화 · 공공문화정보 연계</t>
+          <t>Ⅱ. 전략 및 방법론 &gt; 3.4.2 웹 접근성 품질마크 · DB 표준화 · 문화정보 연계</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Ⅱ. 전략 및 방법론 &gt; 3.4.2 웹 접근성 품질인증 · DB 표준화 · 공공문화정보 연계</t>
+          <t>Ⅱ. 전략 및 방법론 &gt; 3.4.2 웹 접근성 품질마크 · DB 표준화 · 문화정보 연계</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Ⅱ. 전략 및 방법론 &gt; 3.3.2 복합장애 합동 대응 및 장애 예방
-Ⅱ. 전략 및 방법론 &gt; 3.4.2 웹 접근성 품질인증 · DB 표준화 · 공공문화정보 연계
+Ⅱ. 전략 및 방법론 &gt; 3.4.2 웹 접근성 품질마크 · DB 표준화 · 문화정보 연계
 Ⅲ. 사업관리 부문 &gt; 3.2.1 소스 · 산출물 형상관리 및 배포
 Ⅲ. 사업관리 부문 &gt; 4.1.1 품질보증 조직 · 방법 · 절차
 Ⅲ. 사업관리 부문 &gt; 9.1.1 전자적 사업진척관리 · EA 관리 · 지침 준수</t>
